--- a/public/downloads/SarkerMechanistic2024.xlsx
+++ b/public/downloads/SarkerMechanistic2024.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="53">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>OH</t>
@@ -653,10 +676,10 @@
         <v>64</v>
       </c>
       <c r="N3" s="5">
-        <v>336.7693476676941</v>
+        <v>336769.3476676941</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03413087540971867</v>
+        <v>34.13087540971867</v>
       </c>
       <c r="P3" s="5">
         <v>9867</v>
@@ -703,10 +726,10 @@
         <v>64</v>
       </c>
       <c r="N4" s="5">
-        <v>974.1370787620544</v>
+        <v>974137.0787620544</v>
       </c>
       <c r="O4" s="4">
-        <v>0.08164072064717184</v>
+        <v>81.64072064717185</v>
       </c>
       <c r="P4" s="5">
         <v>11932</v>
@@ -753,10 +776,10 @@
         <v>64</v>
       </c>
       <c r="N5" s="5">
-        <v>1369.547399520874</v>
+        <v>1369547.399520874</v>
       </c>
       <c r="O5" s="4">
-        <v>0.141088637016676</v>
+        <v>141.088637016676</v>
       </c>
       <c r="P5" s="5">
         <v>9707</v>
@@ -803,10 +826,10 @@
         <v>64</v>
       </c>
       <c r="N6" s="5">
-        <v>1180.419459819794</v>
+        <v>1180419.459819794</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08856024156499315</v>
+        <v>88.56024156499315</v>
       </c>
       <c r="P6" s="5">
         <v>13329</v>
@@ -853,10 +876,10 @@
         <v>64</v>
       </c>
       <c r="N7" s="5">
-        <v>1466.45081281662</v>
+        <v>1466450.81281662</v>
       </c>
       <c r="O7" s="4">
-        <v>0.3431096894751099</v>
+        <v>343.10968947511</v>
       </c>
       <c r="P7" s="5">
         <v>4274</v>
@@ -903,10 +926,10 @@
         <v>64</v>
       </c>
       <c r="N8" s="5">
-        <v>211.2540819644928</v>
+        <v>211254.0819644928</v>
       </c>
       <c r="O8" s="4">
-        <v>0.02082141552971543</v>
+        <v>20.82141552971543</v>
       </c>
       <c r="P8" s="5">
         <v>10146</v>
@@ -953,10 +976,10 @@
         <v>64</v>
       </c>
       <c r="N9" s="5">
-        <v>405.105476140976</v>
+        <v>405105.476140976</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03249422283957455</v>
+        <v>32.49422283957455</v>
       </c>
       <c r="P9" s="5">
         <v>12467</v>
@@ -1003,10 +1026,10 @@
         <v>64</v>
       </c>
       <c r="N10" s="5">
-        <v>518.6922628879547</v>
+        <v>518692.2628879547</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08653524572705283</v>
+        <v>86.53524572705282</v>
       </c>
       <c r="P10" s="5">
         <v>5994</v>
@@ -1053,10 +1076,10 @@
         <v>64</v>
       </c>
       <c r="N11" s="5">
-        <v>410.0065889358521</v>
+        <v>410006.5889358521</v>
       </c>
       <c r="O11" s="4">
-        <v>0.0436641734755966</v>
+        <v>43.6641734755966</v>
       </c>
       <c r="P11" s="5">
         <v>9390</v>
@@ -1103,10 +1126,10 @@
         <v>64</v>
       </c>
       <c r="N12" s="5">
-        <v>199.158154964447</v>
+        <v>199158.154964447</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02472171734911209</v>
+        <v>24.72171734911209</v>
       </c>
       <c r="P12" s="5">
         <v>8056</v>
@@ -1153,10 +1176,10 @@
         <v>64</v>
       </c>
       <c r="N13" s="5">
-        <v>995.9840741157532</v>
+        <v>995984.0741157532</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07463909428325488</v>
+        <v>74.63909428325488</v>
       </c>
       <c r="P13" s="5">
         <v>13344</v>
@@ -1203,10 +1226,10 @@
         <v>64</v>
       </c>
       <c r="N14" s="5">
-        <v>3994.754162073135</v>
+        <v>3994754.162073135</v>
       </c>
       <c r="O14" s="4">
-        <v>0.474774680541138</v>
+        <v>474.774680541138</v>
       </c>
       <c r="P14" s="5">
         <v>8414</v>
@@ -1253,10 +1276,10 @@
         <v>64</v>
       </c>
       <c r="N15" s="5">
-        <v>3332.009496212006</v>
+        <v>3332009.496212006</v>
       </c>
       <c r="O15" s="4">
-        <v>0.485928175034564</v>
+        <v>485.928175034564</v>
       </c>
       <c r="P15" s="5">
         <v>6857</v>
@@ -1303,10 +1326,10 @@
         <v>64</v>
       </c>
       <c r="N16" s="5">
-        <v>914.5545253753662</v>
+        <v>914554.5253753662</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1055092899602407</v>
+        <v>105.5092899602407</v>
       </c>
       <c r="P16" s="5">
         <v>8668</v>
@@ -1353,10 +1376,10 @@
         <v>64</v>
       </c>
       <c r="N17" s="5">
-        <v>802.7811074256897</v>
+        <v>802781.1074256897</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1065402929562959</v>
+        <v>106.5402929562959</v>
       </c>
       <c r="P17" s="5">
         <v>7535</v>
@@ -1384,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1395,9 +1418,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1431,8 +1460,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1454,50 +1491,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2288582078328707</v>
+        <v>0.296065420177421</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1014059081427198</v>
+        <v>0.1300087258248601</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1030552266367926</v>
+        <v>0.162122214683973</v>
       </c>
       <c r="E3" s="4">
-        <v>93.65114795918366</v>
+        <v>84.83737244897959</v>
       </c>
       <c r="F3" s="4">
-        <v>92.00398489932886</v>
+        <v>80.46140939597315</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.03362915327261311</v>
+      </c>
+      <c r="O3" s="5">
+        <v>42</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2969177268145756</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1297060905446855</v>
+      </c>
+      <c r="R3" s="5">
+        <v>42</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1508,6 +1581,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1515,7 +1589,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1526,9 +1600,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1562,8 +1642,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1585,50 +1673,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1987294693684403</v>
+        <v>0.4299787306444598</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1380828132084169</v>
+        <v>0.1386572012917378</v>
       </c>
       <c r="D3" s="4">
-        <v>0.138640860081634</v>
+        <v>0.1597769448316244</v>
       </c>
       <c r="E3" s="4">
-        <v>86.79900085034014</v>
+        <v>82.31823979591839</v>
       </c>
       <c r="F3" s="4">
-        <v>83.12779642058166</v>
+        <v>78.28631851230422</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.08536877955229502</v>
+      </c>
+      <c r="O3" s="5">
+        <v>38</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4273686645718597</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1380854368804176</v>
+      </c>
+      <c r="R3" s="5">
+        <v>38</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1639,6 +1763,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1646,7 +1771,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1657,9 +1782,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1693,8 +1824,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1716,50 +1855,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2864220980412346</v>
+        <v>0.2288582078328707</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1320498122560695</v>
+        <v>0.1014059081427198</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1754677141284224</v>
+        <v>0.1030552266367926</v>
       </c>
       <c r="E3" s="4">
-        <v>89.1204294217687</v>
+        <v>93.65114795918366</v>
       </c>
       <c r="F3" s="4">
-        <v>87.68963227069347</v>
+        <v>92.00398489932886</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I3" s="5">
         <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.06477237736104355</v>
+      </c>
+      <c r="O3" s="5">
+        <v>54</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2319671252802196</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1003209756509918</v>
+      </c>
+      <c r="R3" s="5">
+        <v>54</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1770,6 +1945,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1777,7 +1953,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1788,9 +1964,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1824,8 +2006,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1847,40 +2037,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5272961282289144</v>
+        <v>0.1987294693684403</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2587716610018039</v>
+        <v>0.1380828132084169</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2215022628270757</v>
+        <v>0.138640860081634</v>
       </c>
       <c r="E3" s="4">
-        <v>86.34141156462573</v>
+        <v>86.79900085034014</v>
       </c>
       <c r="F3" s="4">
-        <v>83.06138143176933</v>
+        <v>83.12779642058166</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>16</v>
@@ -1888,9 +2096,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.05809339198160875</v>
+      </c>
+      <c r="O3" s="5">
+        <v>48</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2052952403934748</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1401118688015427</v>
+      </c>
+      <c r="R3" s="5">
+        <v>48</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1901,6 +2127,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1908,7 +2135,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1919,9 +2146,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1955,8 +2188,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1978,25 +2219,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3635121261724544</v>
+        <v>0.2864220980412346</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1873818815679235</v>
+        <v>0.1320498122560695</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2002379871518537</v>
+        <v>0.1754677141284224</v>
       </c>
       <c r="E3" s="4">
-        <v>83.41517857142857</v>
+        <v>89.1204294217687</v>
       </c>
       <c r="F3" s="4">
-        <v>84.74954558165547</v>
+        <v>87.68963227069347</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
@@ -2005,23 +2264,41 @@
         <v>48</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.1190375362727885</v>
+      </c>
+      <c r="O3" s="5">
+        <v>48</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.250785921911673</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08891603875983645</v>
+      </c>
+      <c r="R3" s="5">
+        <v>48</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2032,6 +2309,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2039,7 +2317,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2050,9 +2328,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2086,8 +2370,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2109,40 +2401,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5918624332404293</v>
+        <v>0.5272961282289144</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4779367823212193</v>
+        <v>0.2587716610018039</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4848272189884277</v>
+        <v>0.2215022628270757</v>
       </c>
       <c r="E3" s="4">
-        <v>92.12903911564625</v>
+        <v>86.34141156462573</v>
       </c>
       <c r="F3" s="4">
-        <v>87.67792225950784</v>
+        <v>83.06138143176933</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
         <v>16</v>
@@ -2150,9 +2460,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.247576189980816</v>
+      </c>
+      <c r="O3" s="5">
+        <v>46</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4082007038639515</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09298531022123482</v>
+      </c>
+      <c r="R3" s="5">
+        <v>46</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2163,6 +2491,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2170,7 +2499,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2181,9 +2510,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2217,8 +2552,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2240,34 +2583,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4305123322224113</v>
+        <v>0.3635121261724544</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2333910113986215</v>
+        <v>0.1873818815679235</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2616165912996175</v>
+        <v>0.2002379871518537</v>
       </c>
       <c r="E3" s="4">
-        <v>82.93526785714288</v>
+        <v>83.41517857142857</v>
       </c>
       <c r="F3" s="4">
-        <v>85.4337947427293</v>
+        <v>84.74954558165547</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
         <v>12</v>
@@ -2281,9 +2642,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.1868050156495643</v>
+      </c>
+      <c r="O3" s="5">
+        <v>48</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.281659946739492</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0884691495177472</v>
+      </c>
+      <c r="R3" s="5">
+        <v>48</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2294,6 +2673,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2301,7 +2681,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2312,9 +2692,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2348,8 +2734,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2371,50 +2765,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4004587552963798</v>
+        <v>0.5918624332404293</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2752271202772135</v>
+        <v>0.4779367823212193</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2845089123039377</v>
+        <v>0.4848272189884277</v>
       </c>
       <c r="E3" s="4">
-        <v>89.42017431972789</v>
+        <v>92.12903911564625</v>
       </c>
       <c r="F3" s="4">
-        <v>85.89293204697985</v>
+        <v>87.67792225950784</v>
       </c>
       <c r="G3" s="5">
         <v>64</v>
       </c>
       <c r="H3" s="5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.4779367823212193</v>
+      </c>
+      <c r="O3" s="5">
+        <v>48</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2012698031551131</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0580866237397832</v>
+      </c>
+      <c r="R3" s="5">
+        <v>48</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2425,12 +2855,1234 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4305123322224113</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2333910113986215</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2616165912996175</v>
+      </c>
+      <c r="E3" s="4">
+        <v>82.93526785714288</v>
+      </c>
+      <c r="F3" s="4">
+        <v>85.4337947427293</v>
+      </c>
+      <c r="G3" s="5">
+        <v>64</v>
+      </c>
+      <c r="H3" s="5">
+        <v>50</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>12</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>12</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.2333910113986215</v>
+      </c>
+      <c r="O3" s="5">
+        <v>50</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3455506689446205</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1317827866813074</v>
+      </c>
+      <c r="R3" s="5">
+        <v>50</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4004587552963798</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2752271202772135</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2845089123039377</v>
+      </c>
+      <c r="E3" s="4">
+        <v>89.42017431972789</v>
+      </c>
+      <c r="F3" s="4">
+        <v>85.89293204697985</v>
+      </c>
+      <c r="G3" s="5">
+        <v>64</v>
+      </c>
+      <c r="H3" s="5">
+        <v>46</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>18</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>18</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2752271202772135</v>
+      </c>
+      <c r="O3" s="5">
+        <v>46</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2539858034953691</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09757312284528864</v>
+      </c>
+      <c r="R3" s="5">
+        <v>46</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="C3" s="3">
+        <v>9.375</v>
+      </c>
+      <c r="D3" s="3">
+        <v>34.375</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>34.375</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.2776950944706231</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1665686378081598</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1887357358333459</v>
+      </c>
+      <c r="K3" s="4">
+        <v>87.81143707482993</v>
+      </c>
+      <c r="L3" s="4">
+        <v>79.38688478747197</v>
+      </c>
+      <c r="M3" s="5">
+        <v>64</v>
+      </c>
+      <c r="N3" s="5">
+        <v>336769.3476676941</v>
+      </c>
+      <c r="O3" s="4">
+        <v>34.13087540971867</v>
+      </c>
+      <c r="P3" s="5">
+        <v>9867</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>59.375</v>
+      </c>
+      <c r="C4" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>34.375</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>34.375</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.3431819093352206</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.1705930493928381</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2198029657779518</v>
+      </c>
+      <c r="K4" s="4">
+        <v>82.71364795918367</v>
+      </c>
+      <c r="L4" s="4">
+        <v>78.40918624161066</v>
+      </c>
+      <c r="M4" s="5">
+        <v>64</v>
+      </c>
+      <c r="N4" s="5">
+        <v>974137.0787620544</v>
+      </c>
+      <c r="O4" s="4">
+        <v>81.64072064717185</v>
+      </c>
+      <c r="P4" s="5">
+        <v>11932</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>65.625</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>34.375</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>34.375</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.2922747842971645</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.09975604188959936</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.1614844966918271</v>
+      </c>
+      <c r="K5" s="4">
+        <v>84.89317602040818</v>
+      </c>
+      <c r="L5" s="4">
+        <v>82.87506991051454</v>
+      </c>
+      <c r="M5" s="5">
+        <v>64</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1369547.399520874</v>
+      </c>
+      <c r="O5" s="4">
+        <v>141.088637016676</v>
+      </c>
+      <c r="P5" s="5">
+        <v>9707</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.2749077441404422</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.09921010508828318</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1065341483010878</v>
+      </c>
+      <c r="K6" s="4">
+        <v>81.04485544217692</v>
+      </c>
+      <c r="L6" s="4">
+        <v>75.06886185682325</v>
+      </c>
+      <c r="M6" s="5">
+        <v>64</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1180419.459819794</v>
+      </c>
+      <c r="O6" s="4">
+        <v>88.56024156499315</v>
+      </c>
+      <c r="P6" s="5">
+        <v>13329</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>81.25</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.1274955226268623</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.06671187858312168</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.06973401457928473</v>
+      </c>
+      <c r="K7" s="4">
+        <v>95.11107568027211</v>
+      </c>
+      <c r="L7" s="4">
+        <v>93.88999580536913</v>
+      </c>
+      <c r="M7" s="5">
+        <v>64</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1466450.81281662</v>
+      </c>
+      <c r="O7" s="4">
+        <v>343.10968947511</v>
+      </c>
+      <c r="P7" s="5">
+        <v>4274</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>65.625</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>34.375</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>34.375</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.2969177268145756</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1297060905446855</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.1689672800190473</v>
+      </c>
+      <c r="K8" s="4">
+        <v>84.83737244897959</v>
+      </c>
+      <c r="L8" s="4">
+        <v>80.46140939597315</v>
+      </c>
+      <c r="M8" s="5">
+        <v>64</v>
+      </c>
+      <c r="N8" s="5">
+        <v>211254.0819644928</v>
+      </c>
+      <c r="O8" s="4">
+        <v>20.82141552971543</v>
+      </c>
+      <c r="P8" s="5">
+        <v>10146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>59.375</v>
+      </c>
+      <c r="C9" s="3">
+        <v>3.125</v>
+      </c>
+      <c r="D9" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.4273686645718597</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.1380854368804176</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.1651998908251386</v>
+      </c>
+      <c r="K9" s="4">
+        <v>82.31823979591839</v>
+      </c>
+      <c r="L9" s="4">
+        <v>78.28631851230422</v>
+      </c>
+      <c r="M9" s="5">
+        <v>64</v>
+      </c>
+      <c r="N9" s="5">
+        <v>405105.476140976</v>
+      </c>
+      <c r="O9" s="4">
+        <v>32.49422283957455</v>
+      </c>
+      <c r="P9" s="5">
+        <v>12467</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>84.375</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3.125</v>
+      </c>
+      <c r="D10" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.2319671252802196</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1003209756509918</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1051370117868879</v>
+      </c>
+      <c r="K10" s="4">
+        <v>93.65114795918366</v>
+      </c>
+      <c r="L10" s="4">
+        <v>92.00398489932886</v>
+      </c>
+      <c r="M10" s="5">
+        <v>64</v>
+      </c>
+      <c r="N10" s="5">
+        <v>518692.2628879547</v>
+      </c>
+      <c r="O10" s="4">
+        <v>86.53524572705282</v>
+      </c>
+      <c r="P10" s="5">
+        <v>5994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>75</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>25</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>25</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.2052952403934748</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1401118688015427</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1495191188081879</v>
+      </c>
+      <c r="K11" s="4">
+        <v>86.79900085034014</v>
+      </c>
+      <c r="L11" s="4">
+        <v>83.12779642058166</v>
+      </c>
+      <c r="M11" s="5">
+        <v>64</v>
+      </c>
+      <c r="N11" s="5">
+        <v>410006.5889358521</v>
+      </c>
+      <c r="O11" s="4">
+        <v>43.6641734755966</v>
+      </c>
+      <c r="P11" s="5">
+        <v>9390</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>75</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3.125</v>
+      </c>
+      <c r="D12" s="3">
+        <v>21.875</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>21.875</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.250785921911673</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.08891603875983645</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1328734838708518</v>
+      </c>
+      <c r="K12" s="4">
+        <v>89.1204294217687</v>
+      </c>
+      <c r="L12" s="4">
+        <v>87.68963227069347</v>
+      </c>
+      <c r="M12" s="5">
+        <v>64</v>
+      </c>
+      <c r="N12" s="5">
+        <v>199158.154964447</v>
+      </c>
+      <c r="O12" s="4">
+        <v>24.72171734911209</v>
+      </c>
+      <c r="P12" s="5">
+        <v>8056</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>71.875</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>28.125</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3.125</v>
+      </c>
+      <c r="F13" s="3">
+        <v>25</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.4082007038639515</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.09298531022123482</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1222291569097675</v>
+      </c>
+      <c r="K13" s="4">
+        <v>86.34141156462573</v>
+      </c>
+      <c r="L13" s="4">
+        <v>83.06138143176933</v>
+      </c>
+      <c r="M13" s="5">
+        <v>64</v>
+      </c>
+      <c r="N13" s="5">
+        <v>995984.0741157532</v>
+      </c>
+      <c r="O13" s="4">
+        <v>74.63909428325488</v>
+      </c>
+      <c r="P13" s="5">
+        <v>13344</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>75</v>
+      </c>
+      <c r="C14" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D14" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.281659946739492</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.0884691495177472</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.09852480939691896</v>
+      </c>
+      <c r="K14" s="4">
+        <v>83.41517857142857</v>
+      </c>
+      <c r="L14" s="4">
+        <v>84.74954558165547</v>
+      </c>
+      <c r="M14" s="5">
+        <v>64</v>
+      </c>
+      <c r="N14" s="5">
+        <v>3994754.162073135</v>
+      </c>
+      <c r="O14" s="4">
+        <v>474.774680541138</v>
+      </c>
+      <c r="P14" s="5">
+        <v>8414</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>75</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>25</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.2012698031551131</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.0580866237397832</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.05727012461610906</v>
+      </c>
+      <c r="K15" s="4">
+        <v>92.12903911564625</v>
+      </c>
+      <c r="L15" s="4">
+        <v>87.67792225950784</v>
+      </c>
+      <c r="M15" s="5">
+        <v>64</v>
+      </c>
+      <c r="N15" s="5">
+        <v>3332009.496212006</v>
+      </c>
+      <c r="O15" s="4">
+        <v>485.928175034564</v>
+      </c>
+      <c r="P15" s="5">
+        <v>6857</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>78.125</v>
+      </c>
+      <c r="C16" s="3">
+        <v>3.125</v>
+      </c>
+      <c r="D16" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.3455506689446205</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.1317827866813074</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.1384953357398557</v>
+      </c>
+      <c r="K16" s="4">
+        <v>82.93526785714288</v>
+      </c>
+      <c r="L16" s="4">
+        <v>85.4337947427293</v>
+      </c>
+      <c r="M16" s="5">
+        <v>64</v>
+      </c>
+      <c r="N16" s="5">
+        <v>914554.5253753662</v>
+      </c>
+      <c r="O16" s="4">
+        <v>105.5092899602407</v>
+      </c>
+      <c r="P16" s="5">
+        <v>8668</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>71.875</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>28.125</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>28.125</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.2539858034953691</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.09757312284528864</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1149368308467874</v>
+      </c>
+      <c r="K17" s="4">
+        <v>89.42017431972789</v>
+      </c>
+      <c r="L17" s="4">
+        <v>85.89293204697985</v>
+      </c>
+      <c r="M17" s="5">
+        <v>64</v>
+      </c>
+      <c r="N17" s="5">
+        <v>802781.1074256897</v>
+      </c>
+      <c r="O17" s="4">
+        <v>106.5402929562959</v>
+      </c>
+      <c r="P17" s="5">
+        <v>7535</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2990,10 +4642,10 @@
         <v>10</v>
       </c>
       <c r="M13" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25" customHeight="1">
@@ -3185,9 +4837,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>36</v>
+      </c>
+      <c r="C3" s="5">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5">
+        <v>22</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>22</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>6</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>38</v>
+      </c>
+      <c r="C4" s="5">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5">
+        <v>22</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>22</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>8</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>42</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>22</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>22</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>14</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>40</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>24</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>24</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>12</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>52</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>12</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>6</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>42</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>22</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>22</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>12</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>38</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>24</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>24</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>10</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>54</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5">
+        <v>8</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>8</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>2</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>48</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>16</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>16</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>8</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>48</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5">
+        <v>14</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>14</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>6</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>18</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2</v>
+      </c>
+      <c r="F13" s="5">
+        <v>16</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>2</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>2</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>10</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>48</v>
+      </c>
+      <c r="C14" s="5">
+        <v>4</v>
+      </c>
+      <c r="D14" s="5">
+        <v>12</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>12</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>4</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>48</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>16</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>16</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>8</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>50</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5">
+        <v>12</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>12</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>6</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>18</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>18</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>10</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3198,9 +5605,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3234,8 +5647,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3257,10 +5678,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.291698332805562</v>
@@ -3298,9 +5737,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.1596914420235215</v>
+      </c>
+      <c r="O3" s="5">
+        <v>36</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2776950944706231</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1665686378081598</v>
+      </c>
+      <c r="R3" s="5">
+        <v>36</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3311,14 +5768,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3329,9 +5787,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3365,8 +5829,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3388,10 +5860,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3830994504425904</v>
@@ -3429,9 +5919,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>0.1132437946661214</v>
+      </c>
+      <c r="O3" s="5">
+        <v>38</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3431819093352206</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1705930493928381</v>
+      </c>
+      <c r="R3" s="5">
+        <v>38</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3442,14 +5950,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3460,9 +5969,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3496,8 +6011,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3519,10 +6042,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3533156713940455</v>
@@ -3560,9 +6101,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.1910632665317646</v>
+      </c>
+      <c r="O3" s="5">
+        <v>42</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2922747842971645</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09975604188959936</v>
+      </c>
+      <c r="R3" s="5">
+        <v>42</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3573,14 +6132,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3591,9 +6151,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3627,8 +6193,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3650,10 +6224,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3437537244076507</v>
@@ -3691,9 +6283,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.1783302080329577</v>
+      </c>
+      <c r="O3" s="5">
+        <v>40</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2749077441404422</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09921010508828318</v>
+      </c>
+      <c r="R3" s="5">
+        <v>40</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3704,14 +6314,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3722,9 +6333,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3758,8 +6375,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3781,10 +6406,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.1383068317290528</v>
@@ -3822,9 +6465,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.04911987180128873</v>
+      </c>
+      <c r="O3" s="5">
+        <v>52</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1274955226268623</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06671187858312168</v>
+      </c>
+      <c r="R3" s="5">
+        <v>52</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3835,268 +6496,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.296065420177421</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1300087258248601</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.162122214683973</v>
-      </c>
-      <c r="E3" s="4">
-        <v>84.83737244897959</v>
-      </c>
-      <c r="F3" s="4">
-        <v>80.46140939597315</v>
-      </c>
-      <c r="G3" s="5">
-        <v>64</v>
-      </c>
-      <c r="H3" s="5">
-        <v>42</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>22</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>22</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4299787306444598</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1386572012917378</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1597769448316244</v>
-      </c>
-      <c r="E3" s="4">
-        <v>82.31823979591839</v>
-      </c>
-      <c r="F3" s="4">
-        <v>78.28631851230422</v>
-      </c>
-      <c r="G3" s="5">
-        <v>64</v>
-      </c>
-      <c r="H3" s="5">
-        <v>38</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>24</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>24</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/SarkerMechanistic2024.xlsx
+++ b/public/downloads/SarkerMechanistic2024.xlsx
@@ -1551,16 +1551,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.03362915327261311</v>
+        <v>-0.01670440058150646</v>
       </c>
       <c r="O3" s="5">
         <v>42</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2969177268145756</v>
+        <v>0.2952876361020441</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1297060905446855</v>
+        <v>0.1280280833965948</v>
       </c>
       <c r="R3" s="5">
         <v>42</v>
@@ -1733,16 +1733,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.08536877955229502</v>
+        <v>-0.03613411829408619</v>
       </c>
       <c r="O3" s="5">
         <v>38</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4273686645718597</v>
+        <v>0.4206435184936534</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1380854368804176</v>
+        <v>0.1323308921648911</v>
       </c>
       <c r="R3" s="5">
         <v>38</v>
@@ -1915,16 +1915,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.06477237736104355</v>
+        <v>-0.03969838303115125</v>
       </c>
       <c r="O3" s="5">
         <v>54</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2319671252802196</v>
+        <v>0.2269884476766073</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1003209756509918</v>
+        <v>0.09720632008336522</v>
       </c>
       <c r="R3" s="5">
         <v>54</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05809339198160875</v>
+        <v>-0.01536234694582106</v>
       </c>
       <c r="O3" s="5">
         <v>48</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2052952403934748</v>
+        <v>0.1981120254772968</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1401118688015427</v>
+        <v>0.1359793591080738</v>
       </c>
       <c r="R3" s="5">
         <v>48</v>
@@ -2279,16 +2279,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1190375362727885</v>
+        <v>-0.108413607863767</v>
       </c>
       <c r="O3" s="5">
         <v>48</v>
       </c>
       <c r="P3" s="4">
-        <v>0.250785921911673</v>
+        <v>0.2506680895794693</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08891603875983645</v>
+        <v>0.08875892898356479</v>
       </c>
       <c r="R3" s="5">
         <v>48</v>
@@ -2461,16 +2461,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.247576189980816</v>
+        <v>-0.2361014125946213</v>
       </c>
       <c r="O3" s="5">
         <v>46</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4082007038639515</v>
+        <v>0.4070507798889187</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09298531022123482</v>
+        <v>0.09188431935971933</v>
       </c>
       <c r="R3" s="5">
         <v>46</v>
@@ -2643,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1868050156495643</v>
+        <v>0.1862021085329673</v>
       </c>
       <c r="O3" s="5">
         <v>48</v>
@@ -2825,16 +2825,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4779367823212193</v>
+        <v>-0.4584824674863928</v>
       </c>
       <c r="O3" s="5">
         <v>48</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2012698031551131</v>
+        <v>0.2010083943671989</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0580866237397832</v>
+        <v>0.0562725086131289</v>
       </c>
       <c r="R3" s="5">
         <v>48</v>
@@ -3007,16 +3007,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2333910113986215</v>
+        <v>0.1938391494723666</v>
       </c>
       <c r="O3" s="5">
         <v>50</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3455506689446205</v>
+        <v>0.3416125809291243</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1317827866813074</v>
+        <v>0.1283241084985224</v>
       </c>
       <c r="R3" s="5">
         <v>50</v>
@@ -3189,16 +3189,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2752271202772135</v>
+        <v>-0.2511942801563425</v>
       </c>
       <c r="O3" s="5">
         <v>46</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2539858034953691</v>
+        <v>0.2521752507076327</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09757312284528864</v>
+        <v>0.09400918678753062</v>
       </c>
       <c r="R3" s="5">
         <v>46</v>
@@ -3335,13 +3335,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.2776950944706231</v>
+        <v>0.2676785719372567</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1665686378081598</v>
+        <v>0.1489344898133693</v>
       </c>
       <c r="J3" s="4">
-        <v>0.1887357358333459</v>
+        <v>0.171841948859254</v>
       </c>
       <c r="K3" s="4">
         <v>87.81143707482993</v>
@@ -3385,13 +3385,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.3431819093352206</v>
+        <v>0.343823544065331</v>
       </c>
       <c r="I4" s="4">
-        <v>0.1705930493928381</v>
+        <v>0.1700527254095873</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2198029657779518</v>
+        <v>0.2217278699682828</v>
       </c>
       <c r="K4" s="4">
         <v>82.71364795918367</v>
@@ -3435,13 +3435,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.2922747842971645</v>
+        <v>0.2916457429787185</v>
       </c>
       <c r="I5" s="4">
-        <v>0.09975604188959936</v>
+        <v>0.09927677603893076</v>
       </c>
       <c r="J5" s="4">
-        <v>0.1614844966918271</v>
+        <v>0.160226404276048</v>
       </c>
       <c r="K5" s="4">
         <v>84.89317602040818</v>
@@ -3485,13 +3485,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.2749077441404422</v>
+        <v>0.2752273971051045</v>
       </c>
       <c r="I6" s="4">
-        <v>0.09921010508828318</v>
+        <v>0.09839882308301355</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1065341483010878</v>
+        <v>0.1024006272113089</v>
       </c>
       <c r="K6" s="4">
         <v>81.04485544217692</v>
@@ -3535,13 +3535,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.1274955226268623</v>
+        <v>0.1265769385192916</v>
       </c>
       <c r="I7" s="4">
-        <v>0.06671187858312168</v>
+        <v>0.06558131352765009</v>
       </c>
       <c r="J7" s="4">
-        <v>0.06973401457928473</v>
+        <v>0.06818829339050669</v>
       </c>
       <c r="K7" s="4">
         <v>95.11107568027211</v>
@@ -3585,13 +3585,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.2969177268145756</v>
+        <v>0.2952876361020441</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1297060905446855</v>
+        <v>0.1280280833965948</v>
       </c>
       <c r="J8" s="4">
-        <v>0.1689672800190473</v>
+        <v>0.1647360918462706</v>
       </c>
       <c r="K8" s="4">
         <v>84.83737244897959</v>
@@ -3635,13 +3635,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.4273686645718597</v>
+        <v>0.4206435184936534</v>
       </c>
       <c r="I9" s="4">
-        <v>0.1380854368804176</v>
+        <v>0.1323308921648911</v>
       </c>
       <c r="J9" s="4">
-        <v>0.1651998908251386</v>
+        <v>0.1554724178698761</v>
       </c>
       <c r="K9" s="4">
         <v>82.31823979591839</v>
@@ -3685,13 +3685,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.2319671252802196</v>
+        <v>0.2269884476766073</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1003209756509918</v>
+        <v>0.09720632008336522</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1051370117868879</v>
+        <v>0.1016705198333863</v>
       </c>
       <c r="K10" s="4">
         <v>93.65114795918366</v>
@@ -3735,13 +3735,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.2052952403934748</v>
+        <v>0.1981120254772968</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1401118688015427</v>
+        <v>0.1359793591080738</v>
       </c>
       <c r="J11" s="4">
-        <v>0.1495191188081879</v>
+        <v>0.1396010067657478</v>
       </c>
       <c r="K11" s="4">
         <v>86.79900085034014</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.250785921911673</v>
+        <v>0.2506680895794693</v>
       </c>
       <c r="I12" s="4">
-        <v>0.08891603875983645</v>
+        <v>0.08875892898356479</v>
       </c>
       <c r="J12" s="4">
-        <v>0.1328734838708518</v>
+        <v>0.1333335823503141</v>
       </c>
       <c r="K12" s="4">
         <v>89.1204294217687</v>
@@ -3835,13 +3835,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.4082007038639515</v>
+        <v>0.4070507798889187</v>
       </c>
       <c r="I13" s="4">
-        <v>0.09298531022123482</v>
+        <v>0.09188431935971933</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1222291569097675</v>
+        <v>0.1179811288095527</v>
       </c>
       <c r="K13" s="4">
         <v>86.34141156462573</v>
@@ -3891,7 +3891,7 @@
         <v>0.0884691495177472</v>
       </c>
       <c r="J14" s="4">
-        <v>0.09852480939691896</v>
+        <v>0.09856249109170626</v>
       </c>
       <c r="K14" s="4">
         <v>83.41517857142857</v>
@@ -3935,13 +3935,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.2012698031551131</v>
+        <v>0.2010083943671989</v>
       </c>
       <c r="I15" s="4">
-        <v>0.0580866237397832</v>
+        <v>0.0562725086131289</v>
       </c>
       <c r="J15" s="4">
-        <v>0.05727012461610906</v>
+        <v>0.05946731213235656</v>
       </c>
       <c r="K15" s="4">
         <v>92.12903911564625</v>
@@ -3985,13 +3985,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.3455506689446205</v>
+        <v>0.3416125809291243</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1317827866813074</v>
+        <v>0.1283241084985224</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1384953357398557</v>
+        <v>0.1401019587227688</v>
       </c>
       <c r="K16" s="4">
         <v>82.93526785714288</v>
@@ -4035,13 +4035,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.2539858034953691</v>
+        <v>0.2521752507076327</v>
       </c>
       <c r="I17" s="4">
-        <v>0.09757312284528864</v>
+        <v>0.09400918678753062</v>
       </c>
       <c r="J17" s="4">
-        <v>0.1149368308467874</v>
+        <v>0.1127902690243296</v>
       </c>
       <c r="K17" s="4">
         <v>89.42017431972789</v>
@@ -5738,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1596914420235215</v>
+        <v>-0.06000374011595966</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2776950944706231</v>
+        <v>0.2676785719372567</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1665686378081598</v>
+        <v>0.1489344898133693</v>
       </c>
       <c r="R3" s="5">
         <v>36</v>
@@ -5920,16 +5920,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1132437946661214</v>
+        <v>0.1029776389843562</v>
       </c>
       <c r="O3" s="5">
         <v>38</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3431819093352206</v>
+        <v>0.343823544065331</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1705930493928381</v>
+        <v>0.1700527254095873</v>
       </c>
       <c r="R3" s="5">
         <v>38</v>
@@ -6102,16 +6102,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1910632665317646</v>
+        <v>-0.1809985272055314</v>
       </c>
       <c r="O3" s="5">
         <v>42</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2922747842971645</v>
+        <v>0.2916457429787185</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09975604188959936</v>
+        <v>0.09927677603893076</v>
       </c>
       <c r="R3" s="5">
         <v>42</v>
@@ -6284,16 +6284,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1783302080329577</v>
+        <v>-0.1651029405456654</v>
       </c>
       <c r="O3" s="5">
         <v>40</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2749077441404422</v>
+        <v>0.2752273971051045</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09921010508828318</v>
+        <v>0.09839882308301355</v>
       </c>
       <c r="R3" s="5">
         <v>40</v>
@@ -6466,16 +6466,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04911987180128873</v>
+        <v>-0.05732509192749546</v>
       </c>
       <c r="O3" s="5">
         <v>52</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1274955226268623</v>
+        <v>0.1265769385192916</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06671187858312168</v>
+        <v>0.06558131352765009</v>
       </c>
       <c r="R3" s="5">
         <v>52</v>
